--- a/data/extraction_mm_251105.xlsx
+++ b/data/extraction_mm_251105.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff2fba3d3057d582/Github repos/Music_on_anxiety_depression_meta_analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6544" documentId="8_{069A1E92-6A17-4742-A179-A8BD204F6CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E0E0D76-44DB-4405-8654-899DF6839D5E}"/>
+  <xr:revisionPtr revIDLastSave="6545" documentId="8_{069A1E92-6A17-4742-A179-A8BD204F6CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89FAA3BE-E731-47CB-B96D-FF08B07F7B46}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="930" yWindow="2970" windowWidth="28800" windowHeight="15370" activeTab="1" xr2:uid="{63CF1AEA-BDD1-4AC6-B12A-ECAC64971320}"/>
+    <workbookView minimized="1" xWindow="42570" yWindow="2670" windowWidth="28800" windowHeight="15370" activeTab="1" xr2:uid="{63CF1AEA-BDD1-4AC6-B12A-ECAC64971320}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
@@ -4305,10 +4305,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B29474E8-A2DE-45C5-8D0A-61E0E8DC691E}" name="Table2" displayName="Table2" ref="A1:A3" totalsRowShown="0">
   <autoFilter ref="A1:A3" xr:uid="{B29474E8-A2DE-45C5-8D0A-61E0E8DC691E}"/>
@@ -5528,6 +5524,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D97D0492-E436-439A-88B9-D72064907446}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:CL300"/>
   <sheetFormatPr defaultColWidth="20.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -5892,7 +5889,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="2" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>325</v>
       </c>
@@ -6105,7 +6102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>326</v>
       </c>
@@ -6315,7 +6312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>327</v>
       </c>
@@ -6525,7 +6522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>328</v>
       </c>
@@ -6738,7 +6735,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>329</v>
       </c>
@@ -6951,7 +6948,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>330</v>
       </c>
@@ -7161,7 +7158,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>356</v>
       </c>
@@ -7374,7 +7371,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>357</v>
       </c>
@@ -7587,7 +7584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>358</v>
       </c>
@@ -7800,7 +7797,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>359</v>
       </c>
@@ -8010,7 +8007,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>379</v>
       </c>
@@ -8217,7 +8214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>380</v>
       </c>
@@ -8424,7 +8421,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>381</v>
       </c>
@@ -8631,7 +8628,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>382</v>
       </c>
@@ -8844,7 +8841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>383</v>
       </c>
@@ -9054,7 +9051,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>384</v>
       </c>
@@ -9264,7 +9261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>385</v>
       </c>
@@ -9474,7 +9471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>386</v>
       </c>
@@ -9687,7 +9684,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>399</v>
       </c>
@@ -9900,7 +9897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>400</v>
       </c>
@@ -10107,7 +10104,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>401</v>
       </c>
@@ -10314,7 +10311,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>402</v>
       </c>
@@ -10524,7 +10521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>403</v>
       </c>
@@ -10734,7 +10731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>424</v>
       </c>
@@ -10935,7 +10932,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>425</v>
       </c>
@@ -11136,7 +11133,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>426</v>
       </c>
@@ -11337,7 +11334,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>427</v>
       </c>
@@ -11538,7 +11535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>428</v>
       </c>
@@ -11754,7 +11751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>429</v>
       </c>
@@ -11970,7 +11967,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>430</v>
       </c>
@@ -12186,7 +12183,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>431</v>
       </c>
@@ -12402,7 +12399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>583</v>
       </c>
@@ -12609,7 +12606,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>584</v>
       </c>
@@ -12813,7 +12810,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>585</v>
       </c>
@@ -13017,7 +13014,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>586</v>
       </c>
@@ -13221,7 +13218,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>587</v>
       </c>
@@ -13428,7 +13425,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>588</v>
       </c>
@@ -13632,7 +13629,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>589</v>
       </c>
@@ -13836,7 +13833,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>590</v>
       </c>
@@ -14040,7 +14037,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>591</v>
       </c>
@@ -14247,7 +14244,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>592</v>
       </c>
@@ -14454,7 +14451,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>593</v>
       </c>
@@ -14661,7 +14658,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>594</v>
       </c>
@@ -14868,7 +14865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>595</v>
       </c>
@@ -15075,7 +15072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>596</v>
       </c>
@@ -15282,7 +15279,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>597</v>
       </c>
@@ -15489,7 +15486,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>598</v>
       </c>
@@ -15696,7 +15693,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>599</v>
       </c>
@@ -15903,7 +15900,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>600</v>
       </c>
@@ -16110,7 +16107,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>601</v>
       </c>
@@ -16317,7 +16314,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>602</v>
       </c>
@@ -16524,7 +16521,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>603</v>
       </c>
@@ -16731,7 +16728,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>604</v>
       </c>
@@ -16938,7 +16935,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>605</v>
       </c>
@@ -17145,7 +17142,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>606</v>
       </c>
@@ -17352,7 +17349,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>607</v>
       </c>
@@ -17559,7 +17556,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>608</v>
       </c>
@@ -17766,7 +17763,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>609</v>
       </c>
@@ -17985,7 +17982,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>610</v>
       </c>
@@ -18204,7 +18201,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>611</v>
       </c>
@@ -18411,7 +18408,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>612</v>
       </c>
@@ -18618,7 +18615,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>613</v>
       </c>
@@ -18825,7 +18822,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>614</v>
       </c>
@@ -19047,7 +19044,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>615</v>
       </c>
@@ -19269,7 +19266,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>616</v>
       </c>
@@ -19491,7 +19488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>617</v>
       </c>
@@ -19701,7 +19698,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>618</v>
       </c>
@@ -19911,7 +19908,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>619</v>
       </c>
@@ -20121,7 +20118,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>620</v>
       </c>
@@ -20331,7 +20328,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>621</v>
       </c>
@@ -20556,7 +20553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>622</v>
       </c>
@@ -20781,7 +20778,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>623</v>
       </c>
@@ -21006,7 +21003,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>624</v>
       </c>
@@ -21231,7 +21228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>625</v>
       </c>
@@ -21435,7 +21432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>626</v>
       </c>
@@ -21639,7 +21636,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>627</v>
       </c>
@@ -21855,7 +21852,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>628</v>
       </c>
@@ -22485,7 +22482,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>631</v>
       </c>
@@ -22686,7 +22683,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>632</v>
       </c>
@@ -22902,7 +22899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>633</v>
       </c>
@@ -23106,7 +23103,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>634</v>
       </c>
@@ -23319,7 +23316,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>635</v>
       </c>
@@ -23520,7 +23517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>636</v>
       </c>
@@ -23733,7 +23730,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>637</v>
       </c>
@@ -23937,7 +23934,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>638</v>
       </c>
@@ -24141,7 +24138,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>639</v>
       </c>
@@ -24345,7 +24342,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>640</v>
       </c>
@@ -24549,7 +24546,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>641</v>
       </c>
@@ -24753,7 +24750,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>642</v>
       </c>
@@ -24957,7 +24954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>643</v>
       </c>
@@ -25161,7 +25158,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>644</v>
       </c>
@@ -25365,7 +25362,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>645</v>
       </c>
@@ -25569,7 +25566,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>646</v>
       </c>
@@ -25773,7 +25770,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>647</v>
       </c>
@@ -25977,7 +25974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>648</v>
       </c>
@@ -26181,7 +26178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>649</v>
       </c>
@@ -26385,7 +26382,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>650</v>
       </c>
@@ -26589,7 +26586,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>651</v>
       </c>
@@ -26793,7 +26790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>652</v>
       </c>
@@ -26997,7 +26994,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>653</v>
       </c>
@@ -27201,7 +27198,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>654</v>
       </c>
@@ -27405,7 +27402,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>655</v>
       </c>
@@ -27609,7 +27606,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>656</v>
       </c>
@@ -27813,7 +27810,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>657</v>
       </c>
@@ -28017,7 +28014,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>658</v>
       </c>
@@ -28221,7 +28218,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>659</v>
       </c>
@@ -28425,7 +28422,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>660</v>
       </c>
@@ -28629,7 +28626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>661</v>
       </c>
@@ -28833,7 +28830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>662</v>
       </c>
@@ -29037,7 +29034,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>663</v>
       </c>
@@ -29241,7 +29238,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>664</v>
       </c>
@@ -29445,7 +29442,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>665</v>
       </c>
@@ -29649,7 +29646,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>666</v>
       </c>
@@ -29853,7 +29850,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>667</v>
       </c>
@@ -30057,7 +30054,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>668</v>
       </c>
@@ -30261,7 +30258,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>669</v>
       </c>
@@ -30465,7 +30462,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>670</v>
       </c>
@@ -30669,7 +30666,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>671</v>
       </c>
@@ -30873,7 +30870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>672</v>
       </c>
@@ -31077,7 +31074,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>673</v>
       </c>
@@ -31281,7 +31278,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>674</v>
       </c>
@@ -31485,7 +31482,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>675</v>
       </c>
@@ -31689,7 +31686,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>676</v>
       </c>
@@ -31893,7 +31890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>677</v>
       </c>
@@ -32106,7 +32103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>678</v>
       </c>
@@ -32319,7 +32316,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>679</v>
       </c>
@@ -32529,7 +32526,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>680</v>
       </c>
@@ -32952,7 +32949,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>682</v>
       </c>
@@ -33162,7 +33159,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>683</v>
       </c>
@@ -33366,7 +33363,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="134" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>700</v>
       </c>
@@ -33570,7 +33567,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="135" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>701</v>
       </c>
@@ -33774,7 +33771,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="136" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>702</v>
       </c>
@@ -33978,7 +33975,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="137" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>703</v>
       </c>
@@ -34182,7 +34179,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="138" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>704</v>
       </c>
@@ -34386,7 +34383,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>705</v>
       </c>
@@ -34590,7 +34587,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="140" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>706</v>
       </c>
@@ -34794,7 +34791,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="141" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>707</v>
       </c>
@@ -34998,7 +34995,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>734</v>
       </c>
@@ -35220,7 +35217,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>735</v>
       </c>
@@ -35420,7 +35417,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="144" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>736</v>
       </c>
@@ -35638,7 +35635,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="145" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>737</v>
       </c>
@@ -35838,7 +35835,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="146" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>738</v>
       </c>
@@ -36056,7 +36053,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>739</v>
       </c>
@@ -36256,7 +36253,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="148" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>740</v>
       </c>
@@ -36474,7 +36471,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="149" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>741</v>
       </c>
@@ -36674,7 +36671,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>742</v>
       </c>
@@ -36892,7 +36889,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="151" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>743</v>
       </c>
@@ -37092,7 +37089,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="152" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>744</v>
       </c>
@@ -37310,7 +37307,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="153" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>745</v>
       </c>
@@ -37510,7 +37507,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="154" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>746</v>
       </c>
@@ -37728,7 +37725,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="155" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>770</v>
       </c>
@@ -37929,7 +37926,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>771</v>
       </c>
@@ -38130,7 +38127,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>772</v>
       </c>
@@ -38328,7 +38325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>773</v>
       </c>
@@ -38526,7 +38523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>774</v>
       </c>
@@ -38724,7 +38721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>775</v>
       </c>
@@ -38922,7 +38919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>776</v>
       </c>
@@ -39120,7 +39117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>777</v>
       </c>
@@ -39318,7 +39315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>778</v>
       </c>
@@ -39516,7 +39513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>779</v>
       </c>
@@ -39714,7 +39711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>780</v>
       </c>
@@ -39912,7 +39909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>781</v>
       </c>
@@ -40110,7 +40107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>782</v>
       </c>
@@ -40308,7 +40305,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="168" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>783</v>
       </c>
@@ -40506,7 +40503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>784</v>
       </c>
@@ -40704,7 +40701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>785</v>
       </c>
@@ -40902,7 +40899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>804</v>
       </c>
@@ -41102,7 +41099,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="172" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>805</v>
       </c>
@@ -41302,7 +41299,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>806</v>
       </c>
@@ -41502,7 +41499,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>807</v>
       </c>
@@ -41702,7 +41699,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>808</v>
       </c>
@@ -41902,7 +41899,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>809</v>
       </c>
@@ -42102,7 +42099,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>810</v>
       </c>
@@ -42302,7 +42299,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>811</v>
       </c>
@@ -42502,7 +42499,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>812</v>
       </c>
@@ -42702,7 +42699,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>813</v>
       </c>
@@ -42902,7 +42899,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>814</v>
       </c>
@@ -43102,7 +43099,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>815</v>
       </c>
@@ -43302,7 +43299,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>816</v>
       </c>
@@ -43502,7 +43499,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>817</v>
       </c>
@@ -43702,7 +43699,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="185" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>818</v>
       </c>
@@ -43902,7 +43899,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>819</v>
       </c>
@@ -44102,7 +44099,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="187" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>820</v>
       </c>
@@ -44309,7 +44306,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="188" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>821</v>
       </c>
@@ -44516,7 +44513,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="189" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>846</v>
       </c>
@@ -44720,7 +44717,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="190" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>847</v>
       </c>
@@ -44924,7 +44921,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="191" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>848</v>
       </c>
@@ -45128,7 +45125,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>849</v>
       </c>
@@ -45332,7 +45329,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="193" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>850</v>
       </c>
@@ -45536,7 +45533,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="194" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>851</v>
       </c>
@@ -45740,7 +45737,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="195" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>852</v>
       </c>
@@ -45944,7 +45941,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="196" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>853</v>
       </c>
@@ -46148,7 +46145,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="197" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>854</v>
       </c>
@@ -46352,7 +46349,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>855</v>
       </c>
@@ -46556,7 +46553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="199" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>856</v>
       </c>
@@ -46760,7 +46757,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="200" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>857</v>
       </c>
@@ -46964,7 +46961,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>858</v>
       </c>
@@ -47168,7 +47165,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="202" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>859</v>
       </c>
@@ -47372,7 +47369,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="203" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>860</v>
       </c>
@@ -47576,7 +47573,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="204" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>861</v>
       </c>
@@ -47780,7 +47777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="205" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>862</v>
       </c>
@@ -47984,7 +47981,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="206" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>863</v>
       </c>
@@ -48188,7 +48185,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>881</v>
       </c>
@@ -48403,7 +48400,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>882</v>
       </c>
@@ -48618,7 +48615,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>883</v>
       </c>
@@ -48833,7 +48830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>884</v>
       </c>
@@ -49048,7 +49045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>885</v>
       </c>
@@ -49263,7 +49260,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>886</v>
       </c>
@@ -49478,7 +49475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>887</v>
       </c>
@@ -49693,7 +49690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="214" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>888</v>
       </c>
@@ -49908,7 +49905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>889</v>
       </c>
@@ -50123,7 +50120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="216" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>890</v>
       </c>
@@ -50338,7 +50335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>891</v>
       </c>
@@ -50553,7 +50550,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>892</v>
       </c>
@@ -50768,7 +50765,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="219" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>893</v>
       </c>
@@ -50983,7 +50980,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>894</v>
       </c>
@@ -51198,7 +51195,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>895</v>
       </c>
@@ -51413,7 +51410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="222" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>896</v>
       </c>
@@ -51628,7 +51625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="223" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>913</v>
       </c>
@@ -51835,7 +51832,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="224" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>914</v>
       </c>
@@ -52042,7 +52039,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>944</v>
       </c>
@@ -52240,7 +52237,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="226" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>945</v>
       </c>
@@ -52438,7 +52435,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="227" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>946</v>
       </c>
@@ -52636,7 +52633,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="228" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>947</v>
       </c>
@@ -52834,7 +52831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="229" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>948</v>
       </c>
@@ -53032,7 +53029,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="230" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>949</v>
       </c>
@@ -53230,7 +53227,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="231" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>950</v>
       </c>
@@ -53428,7 +53425,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="232" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>951</v>
       </c>
@@ -53626,7 +53623,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="233" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>952</v>
       </c>
@@ -53824,7 +53821,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="234" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>953</v>
       </c>
@@ -54022,7 +54019,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="235" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>954</v>
       </c>
@@ -54223,7 +54220,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>955</v>
       </c>
@@ -54424,7 +54421,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="237" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>956</v>
       </c>
@@ -54625,7 +54622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>957</v>
       </c>
@@ -54826,7 +54823,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="239" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>967</v>
       </c>
@@ -55027,7 +55024,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>968</v>
       </c>
@@ -55228,7 +55225,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="241" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>969</v>
       </c>
@@ -55429,7 +55426,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="242" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>974</v>
       </c>
@@ -55630,7 +55627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="243" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>975</v>
       </c>
@@ -55831,7 +55828,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="244" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>976</v>
       </c>
@@ -56032,7 +56029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="245" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>977</v>
       </c>
@@ -56233,7 +56230,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="246" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>1025</v>
       </c>
@@ -56431,7 +56428,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="247" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>1026</v>
       </c>
@@ -56632,7 +56629,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="248" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>1027</v>
       </c>
@@ -56830,7 +56827,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="249" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>1028</v>
       </c>
@@ -57028,7 +57025,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="250" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>1029</v>
       </c>
@@ -57226,7 +57223,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="251" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>1030</v>
       </c>
@@ -57424,7 +57421,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="252" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>1031</v>
       </c>
@@ -57622,7 +57619,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="253" spans="1:90" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:90" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>1032</v>
       </c>
@@ -57820,7 +57817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="254" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>1033</v>
       </c>
@@ -58032,7 +58029,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="255" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>1034</v>
       </c>
@@ -58244,7 +58241,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="256" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>1035</v>
       </c>
@@ -58456,7 +58453,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>1036</v>
       </c>
@@ -58668,7 +58665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="258" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>1037</v>
       </c>
@@ -58869,7 +58866,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="259" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>1038</v>
       </c>
@@ -59073,7 +59070,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="260" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>1039</v>
       </c>
@@ -59274,7 +59271,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="261" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>1040</v>
       </c>
@@ -59475,7 +59472,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="262" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>1041</v>
       </c>
@@ -59676,7 +59673,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="263" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>1042</v>
       </c>
@@ -59877,7 +59874,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="264" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>1043</v>
       </c>
@@ -60078,7 +60075,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="265" spans="1:90" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:90" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>1044</v>
       </c>
@@ -60279,7 +60276,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="266" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>1045</v>
       </c>
@@ -60488,7 +60485,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="267" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>1046</v>
       </c>
@@ -60700,7 +60697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="268" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>1047</v>
       </c>
@@ -60909,7 +60906,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="269" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>1048</v>
       </c>
@@ -61118,7 +61115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="270" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>1049</v>
       </c>
@@ -61327,7 +61324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>1050</v>
       </c>
@@ -61536,7 +61533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>1051</v>
       </c>
@@ -61745,7 +61742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>1052</v>
       </c>
@@ -61954,7 +61951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>1053</v>
       </c>
@@ -62163,7 +62160,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="275" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>1054</v>
       </c>
@@ -62372,7 +62369,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="276" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>1055</v>
       </c>
@@ -62584,7 +62581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>1056</v>
       </c>
@@ -62793,7 +62790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>1057</v>
       </c>
@@ -63005,7 +63002,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="279" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>1058</v>
       </c>
@@ -63214,7 +63211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>1059</v>
       </c>
@@ -63423,7 +63420,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="281" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>1060</v>
       </c>
@@ -63632,7 +63629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>1061</v>
       </c>
@@ -63841,7 +63838,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="283" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>1062</v>
       </c>
@@ -64050,7 +64047,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>1063</v>
       </c>
@@ -64259,7 +64256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="285" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>1064</v>
       </c>
@@ -64468,7 +64465,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="286" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>1065</v>
       </c>
@@ -64677,7 +64674,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="287" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>1066</v>
       </c>
@@ -64886,7 +64883,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="288" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>1067</v>
       </c>
@@ -65095,7 +65092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>1068</v>
       </c>
@@ -65304,7 +65301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>1069</v>
       </c>
@@ -65513,7 +65510,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>1070</v>
       </c>
@@ -65722,7 +65719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>1071</v>
       </c>
@@ -65931,7 +65928,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="293" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>1072</v>
       </c>
@@ -66140,7 +66137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="294" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>1073</v>
       </c>
@@ -66349,7 +66346,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="295" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>1074</v>
       </c>
@@ -66558,7 +66555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="296" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>1075</v>
       </c>
@@ -66767,7 +66764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>1076</v>
       </c>
@@ -66976,7 +66973,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>1077</v>
       </c>
@@ -67185,7 +67182,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="299" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>1078</v>
       </c>
@@ -67396,7 +67393,13 @@
     </row>
     <row r="300" spans="1:90" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <autoFilter ref="A1:CL299" xr:uid="{D97D0492-E436-439A-88B9-D72064907446}"/>
+  <autoFilter ref="A1:CL299" xr:uid="{D97D0492-E436-439A-88B9-D72064907446}">
+    <filterColumn colId="53">
+      <filters>
+        <filter val="both"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
